--- a/rtss-pre1917/src/main/resources/csk-dvizhenie-evropriskoi-chasti-rossii/PatchYearData.xlsx
+++ b/rtss-pre1917/src/main/resources/csk-dvizhenie-evropriskoi-chasti-rossii/PatchYearData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\csk-dvizhenie-evropriskoi-chasti-rossii\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-pre1917\src\main\resources\csk-dvizhenie-evropriskoi-chasti-rossii\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BD74FE6-CBF3-46BA-B4F5-6D36F4F84E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2E0D9F3-AED7-4F09-8ED2-3DB164AB90A3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
+    <workbookView xWindow="5565" yWindow="2040" windowWidth="24945" windowHeight="21255" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
   <si>
     <t>год</t>
   </si>
@@ -74,6 +74,24 @@
   </si>
   <si>
     <t>Исправления для значений в томах "Движение население в Европейской России" ЦСК.</t>
+  </si>
+  <si>
+    <t>Астраханская</t>
+  </si>
+  <si>
+    <t>Гродненская</t>
+  </si>
+  <si>
+    <t>Пермская</t>
+  </si>
+  <si>
+    <t>Подольская</t>
+  </si>
+  <si>
+    <t>Таврическая</t>
+  </si>
+  <si>
+    <t>Харьковская</t>
   </si>
 </sst>
 </file>
@@ -121,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -130,6 +148,21 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -148,9 +181,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -188,7 +221,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -294,7 +327,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -436,7 +469,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -445,9 +478,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E727C47-D865-4836-8CF2-7B9647F06C78}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -459,16 +492,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5AD7F50-502A-4E44-B9E1-3028D5075735}">
-  <dimension ref="A1:U40"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:U71"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.89453125" customWidth="1"/>
-    <col min="3" max="3" width="11.68359375" customWidth="1"/>
-    <col min="4" max="5" width="18.26171875" customWidth="1"/>
-    <col min="6" max="6" width="16.68359375" customWidth="1"/>
+    <col min="1" max="1" width="18.85546875" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" customWidth="1"/>
+    <col min="4" max="5" width="18.28515625" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>3</v>
       </c>
@@ -488,290 +521,596 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="1" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="9">
+        <v>1907</v>
+      </c>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10">
+        <v>33399</v>
+      </c>
+      <c r="E3" s="10"/>
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="9">
+        <v>1908</v>
+      </c>
+      <c r="C4" s="10">
+        <v>62846</v>
+      </c>
+      <c r="D4" s="10">
+        <v>39384</v>
+      </c>
+      <c r="E4" s="10"/>
+      <c r="F4" s="7"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="9">
+        <v>1912</v>
+      </c>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10">
+        <v>34926</v>
+      </c>
+      <c r="E5" s="10"/>
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="9">
+        <v>1913</v>
+      </c>
+      <c r="C6" s="10">
+        <v>206461</v>
+      </c>
+      <c r="D6" s="10">
+        <v>154406</v>
+      </c>
+      <c r="E6" s="10"/>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="9">
+        <v>1911</v>
+      </c>
+      <c r="C7" s="10">
+        <v>139919</v>
+      </c>
+      <c r="D7" s="10">
+        <v>94396</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="7"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="9">
+        <v>1882</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="7"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="9">
+        <v>1883</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="7"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="9">
+        <v>1901</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="7"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="9">
+        <v>1903</v>
+      </c>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="7"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="9">
+        <v>1882</v>
+      </c>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10">
+        <v>64226</v>
+      </c>
+      <c r="E12" s="10"/>
+      <c r="F12" s="7"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="6"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="6"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="6"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="6"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="6"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="6"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="6"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="6"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="6"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="6"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="6"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="6"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="6"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="6"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="6"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="6"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="6"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" t="s">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" t="s">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" t="s">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" t="s">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" t="s">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" t="s">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" t="s">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="2"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="2"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="2"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="O15" s="3"/>
-      <c r="P15" s="2"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="2"/>
-    </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="O17" s="3"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="2"/>
-      <c r="T17" s="2"/>
-      <c r="U17" s="2"/>
-    </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-    </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-    </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-    </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-    </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-    </row>
-    <row r="23" spans="2:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-    </row>
-    <row r="24" spans="2:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="5"/>
-      <c r="L24" s="5"/>
-    </row>
-    <row r="25" spans="2:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-    </row>
-    <row r="26" spans="2:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-    </row>
-    <row r="27" spans="2:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="5"/>
-    </row>
-    <row r="28" spans="2:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
-    </row>
-    <row r="29" spans="2:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="O29" s="2"/>
-    </row>
-    <row r="30" spans="2:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
-      <c r="O30" s="2"/>
-    </row>
-    <row r="31" spans="2:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
-      <c r="O31" s="2"/>
-    </row>
-    <row r="32" spans="2:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
-      <c r="O32" s="2"/>
-    </row>
-    <row r="33" spans="11:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="K33" s="5"/>
-      <c r="L33" s="5"/>
-      <c r="O33" s="2"/>
-    </row>
-    <row r="34" spans="11:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="O34" s="2"/>
-    </row>
-    <row r="35" spans="11:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="O35" s="2"/>
-    </row>
-    <row r="36" spans="11:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="O36" s="2"/>
-    </row>
-    <row r="37" spans="11:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="O37" s="2"/>
-    </row>
-    <row r="38" spans="11:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="11:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="O39" s="2"/>
-    </row>
-    <row r="40" spans="11:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="O40" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="O43" s="3"/>
+      <c r="P43" s="2"/>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="L44" s="2"/>
+      <c r="M44" s="2"/>
+      <c r="O44" s="3"/>
+      <c r="P44" s="2"/>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+      <c r="L45" s="2"/>
+      <c r="M45" s="2"/>
+      <c r="O45" s="3"/>
+      <c r="P45" s="2"/>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="L46" s="2"/>
+      <c r="M46" s="2"/>
+      <c r="O46" s="3"/>
+      <c r="P46" s="2"/>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="O47" s="3"/>
+      <c r="P47" s="2"/>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2"/>
+      <c r="L48" s="2"/>
+      <c r="M48" s="2"/>
+      <c r="O48" s="3"/>
+      <c r="P48" s="2"/>
+      <c r="Q48" s="2"/>
+      <c r="T48" s="2"/>
+      <c r="U48" s="2"/>
+    </row>
+    <row r="49" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+    </row>
+    <row r="50" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2"/>
+      <c r="K50" s="2"/>
+      <c r="L50" s="2"/>
+      <c r="M50" s="2"/>
+    </row>
+    <row r="51" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+    </row>
+    <row r="52" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="L52" s="2"/>
+      <c r="M52" s="2"/>
+    </row>
+    <row r="53" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2"/>
+      <c r="L53" s="2"/>
+    </row>
+    <row r="54" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2"/>
+      <c r="L54" s="2"/>
+    </row>
+    <row r="55" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="5"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2"/>
+      <c r="L56" s="2"/>
+    </row>
+    <row r="57" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
+      <c r="K57" s="2"/>
+      <c r="L57" s="2"/>
+    </row>
+    <row r="58" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+      <c r="K58" s="5"/>
+      <c r="L58" s="5"/>
+    </row>
+    <row r="59" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2"/>
+      <c r="L59" s="2"/>
+    </row>
+    <row r="60" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
+      <c r="O60" s="2"/>
+    </row>
+    <row r="61" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2"/>
+      <c r="L61" s="2"/>
+      <c r="O61" s="2"/>
+    </row>
+    <row r="62" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2"/>
+      <c r="L62" s="2"/>
+      <c r="O62" s="2"/>
+    </row>
+    <row r="63" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="2"/>
+      <c r="L63" s="2"/>
+      <c r="O63" s="2"/>
+    </row>
+    <row r="64" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="K64" s="5"/>
+      <c r="L64" s="5"/>
+      <c r="O64" s="2"/>
+    </row>
+    <row r="65" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O65" s="2"/>
+    </row>
+    <row r="66" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O66" s="2"/>
+    </row>
+    <row r="67" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O67" s="2"/>
+    </row>
+    <row r="68" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O68" s="2"/>
+    </row>
+    <row r="69" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O69" s="2"/>
+    </row>
+    <row r="70" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O70" s="2"/>
+    </row>
+    <row r="71" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O71" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/rtss-pre1917/src/main/resources/csk-dvizhenie-evropriskoi-chasti-rossii/PatchYearData.xlsx
+++ b/rtss-pre1917/src/main/resources/csk-dvizhenie-evropriskoi-chasti-rossii/PatchYearData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-pre1917\src\main\resources\csk-dvizhenie-evropriskoi-chasti-rossii\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2E0D9F3-AED7-4F09-8ED2-3DB164AB90A3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF58A4D7-0D58-4A7A-B564-5B1DAEC751C5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5565" yWindow="2040" windowWidth="24945" windowHeight="21255" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
+    <workbookView xWindow="10890" yWindow="2235" windowWidth="24945" windowHeight="21255" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
   <si>
     <t>год</t>
   </si>
@@ -139,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -162,6 +162,12 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -492,7 +498,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5AD7F50-502A-4E44-B9E1-3028D5075735}">
-  <dimension ref="A1:U71"/>
+  <dimension ref="A1:U76"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.85546875" customWidth="1"/>
@@ -533,28 +539,26 @@
       <c r="A3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="9">
-        <v>1907</v>
-      </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10">
-        <v>33399</v>
-      </c>
-      <c r="E3" s="10"/>
-      <c r="F3" s="7"/>
+      <c r="B3" s="7">
+        <v>1883</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="11">
+        <v>24473</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" s="9">
-        <v>1908</v>
-      </c>
-      <c r="C4" s="10">
-        <v>62846</v>
-      </c>
+        <v>1907</v>
+      </c>
+      <c r="C4" s="10"/>
       <c r="D4" s="10">
-        <v>39384</v>
+        <v>33399</v>
       </c>
       <c r="E4" s="10"/>
       <c r="F4" s="7"/>
@@ -563,148 +567,188 @@
       <c r="A5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="9">
-        <v>1912</v>
-      </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10">
-        <v>34926</v>
+      <c r="B5" s="12">
+        <v>1903</v>
+      </c>
+      <c r="C5" s="2">
+        <v>64955</v>
+      </c>
+      <c r="D5" s="2">
+        <v>46270</v>
       </c>
       <c r="E5" s="10"/>
       <c r="F5" s="7"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="9">
-        <v>1913</v>
-      </c>
-      <c r="C6" s="10">
-        <v>206461</v>
-      </c>
-      <c r="D6" s="10">
-        <v>154406</v>
+        <v>15</v>
+      </c>
+      <c r="B6" s="12">
+        <v>1904</v>
+      </c>
+      <c r="C6" s="2">
+        <v>65477.5</v>
+      </c>
+      <c r="D6" s="2">
+        <v>47868.5</v>
       </c>
       <c r="E6" s="10"/>
       <c r="F6" s="7"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="9">
-        <v>1911</v>
-      </c>
-      <c r="C7" s="10">
-        <v>139919</v>
-      </c>
-      <c r="D7" s="10">
-        <v>94396</v>
+        <v>15</v>
+      </c>
+      <c r="B7" s="12">
+        <v>1905</v>
+      </c>
+      <c r="C7" s="2">
+        <v>65509</v>
+      </c>
+      <c r="D7" s="2">
+        <v>45467.5</v>
       </c>
       <c r="E7" s="10"/>
       <c r="F7" s="7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="9">
-        <v>1882</v>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
+        <v>15</v>
+      </c>
+      <c r="B8" s="12">
+        <v>1906</v>
+      </c>
+      <c r="C8" s="2">
+        <v>66434</v>
+      </c>
+      <c r="D8" s="2">
+        <v>37380.5</v>
+      </c>
       <c r="E8" s="10"/>
       <c r="F8" s="7"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B9" s="9">
-        <v>1883</v>
-      </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
+        <v>1908</v>
+      </c>
+      <c r="C9" s="10">
+        <v>62846</v>
+      </c>
+      <c r="D9" s="10">
+        <v>39384</v>
+      </c>
       <c r="E9" s="10"/>
       <c r="F9" s="7"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B10" s="9">
-        <v>1901</v>
+        <v>1912</v>
       </c>
       <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
+      <c r="D10" s="10">
+        <v>34926</v>
+      </c>
       <c r="E10" s="10"/>
       <c r="F10" s="7"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B11" s="9">
-        <v>1903</v>
-      </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
+        <v>1913</v>
+      </c>
+      <c r="C11" s="10">
+        <v>206461</v>
+      </c>
+      <c r="D11" s="10">
+        <v>154406</v>
+      </c>
       <c r="E11" s="10"/>
       <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B12" s="9">
-        <v>1882</v>
-      </c>
-      <c r="C12" s="10"/>
+        <v>1911</v>
+      </c>
+      <c r="C12" s="10">
+        <v>139919</v>
+      </c>
       <c r="D12" s="10">
-        <v>64226</v>
+        <v>94396</v>
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="7"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="6"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
+      <c r="A13" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="9">
+        <v>1882</v>
+      </c>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
       <c r="F13" s="7"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="6"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
+      <c r="A14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="9">
+        <v>1883</v>
+      </c>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
       <c r="F14" s="7"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="6"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
+      <c r="A15" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="9">
+        <v>1901</v>
+      </c>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
       <c r="F15" s="7"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="6"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
+      <c r="A16" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="9">
+        <v>1903</v>
+      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
       <c r="F16" s="7"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="6"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
+      <c r="A17" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="9">
+        <v>1882</v>
+      </c>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10">
+        <v>64226</v>
+      </c>
+      <c r="E17" s="10"/>
       <c r="F17" s="7"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -812,7 +856,7 @@
       <c r="F30" s="7"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="7"/>
+      <c r="A31" s="6"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
@@ -820,159 +864,146 @@
       <c r="F31" s="7"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="7"/>
+      <c r="A32" s="6"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" s="6"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" s="6"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A35" s="6"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A36" s="7"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A37" s="7"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>10</v>
       </c>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="O43" s="3"/>
-      <c r="P43" s="2"/>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
-      <c r="L44" s="2"/>
-      <c r="M44" s="2"/>
-      <c r="O44" s="3"/>
-      <c r="P44" s="2"/>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
-      <c r="L45" s="2"/>
-      <c r="M45" s="2"/>
-      <c r="O45" s="3"/>
-      <c r="P45" s="2"/>
-    </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-      <c r="L46" s="2"/>
-      <c r="M46" s="2"/>
-      <c r="O46" s="3"/>
-      <c r="P46" s="2"/>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
-      <c r="O47" s="3"/>
-      <c r="P47" s="2"/>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
-      <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-      <c r="K48" s="2"/>
-      <c r="L48" s="2"/>
-      <c r="M48" s="2"/>
       <c r="O48" s="3"/>
       <c r="P48" s="2"/>
-      <c r="Q48" s="2"/>
-      <c r="T48" s="2"/>
-      <c r="U48" s="2"/>
-    </row>
-    <row r="49" spans="2:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
-    </row>
-    <row r="50" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="L49" s="2"/>
+      <c r="M49" s="2"/>
+      <c r="O49" s="3"/>
+      <c r="P49" s="2"/>
+    </row>
+    <row r="50" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
-      <c r="K50" s="2"/>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
-    </row>
-    <row r="51" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="O50" s="3"/>
+      <c r="P50" s="2"/>
+    </row>
+    <row r="51" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
-    </row>
-    <row r="52" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="L51" s="2"/>
+      <c r="M51" s="2"/>
+      <c r="O51" s="3"/>
+      <c r="P51" s="2"/>
+    </row>
+    <row r="52" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
-      <c r="L52" s="2"/>
-      <c r="M52" s="2"/>
-    </row>
-    <row r="53" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="O52" s="3"/>
+      <c r="P52" s="2"/>
+    </row>
+    <row r="53" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
       <c r="G53" s="2"/>
@@ -981,58 +1012,61 @@
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
-    </row>
-    <row r="54" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="M53" s="2"/>
+      <c r="O53" s="3"/>
+      <c r="P53" s="2"/>
+      <c r="Q53" s="2"/>
+      <c r="T53" s="2"/>
+      <c r="U53" s="2"/>
+    </row>
+    <row r="54" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
-      <c r="K54" s="2"/>
-      <c r="L54" s="2"/>
-    </row>
-    <row r="55" spans="2:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
-      <c r="K55" s="5"/>
-      <c r="L55" s="5"/>
-    </row>
-    <row r="56" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="K55" s="2"/>
+      <c r="L55" s="2"/>
+      <c r="M55" s="2"/>
+    </row>
+    <row r="56" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
-      <c r="K56" s="2"/>
-      <c r="L56" s="2"/>
-    </row>
-    <row r="57" spans="2:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
-      <c r="K57" s="2"/>
       <c r="L57" s="2"/>
-    </row>
-    <row r="58" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="M57" s="2"/>
+    </row>
+    <row r="58" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
-      <c r="K58" s="5"/>
-      <c r="L58" s="5"/>
-    </row>
-    <row r="59" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="K58" s="2"/>
+      <c r="L58" s="2"/>
+    </row>
+    <row r="59" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
       <c r="G59" s="2"/>
@@ -1042,16 +1076,17 @@
       <c r="K59" s="2"/>
       <c r="L59" s="2"/>
     </row>
-    <row r="60" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
-      <c r="O60" s="2"/>
-    </row>
-    <row r="61" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="K60" s="5"/>
+      <c r="L60" s="5"/>
+    </row>
+    <row r="61" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
       <c r="G61" s="2"/>
@@ -1060,57 +1095,106 @@
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
       <c r="L61" s="2"/>
-      <c r="O61" s="2"/>
-    </row>
-    <row r="62" spans="2:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
+      <c r="G62" s="2"/>
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
       <c r="L62" s="2"/>
-      <c r="O62" s="2"/>
-    </row>
-    <row r="63" spans="2:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
+      <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
-      <c r="K63" s="2"/>
-      <c r="L63" s="2"/>
-      <c r="O63" s="2"/>
-    </row>
-    <row r="64" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="K64" s="5"/>
-      <c r="L64" s="5"/>
-      <c r="O64" s="2"/>
-    </row>
-    <row r="65" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="K63" s="5"/>
+      <c r="L63" s="5"/>
+    </row>
+    <row r="64" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+      <c r="I64" s="2"/>
+      <c r="J64" s="2"/>
+      <c r="K64" s="2"/>
+      <c r="L64" s="2"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
       <c r="O65" s="2"/>
     </row>
-    <row r="66" spans="15:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2"/>
+      <c r="L66" s="2"/>
       <c r="O66" s="2"/>
     </row>
-    <row r="67" spans="15:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="2"/>
+      <c r="L67" s="2"/>
       <c r="O67" s="2"/>
     </row>
-    <row r="68" spans="15:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
+      <c r="L68" s="2"/>
       <c r="O68" s="2"/>
     </row>
-    <row r="69" spans="15:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="K69" s="5"/>
+      <c r="L69" s="5"/>
       <c r="O69" s="2"/>
     </row>
-    <row r="70" spans="15:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:15" x14ac:dyDescent="0.25">
       <c r="O70" s="2"/>
     </row>
-    <row r="71" spans="15:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:15" x14ac:dyDescent="0.25">
       <c r="O71" s="2"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="O72" s="2"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="O73" s="2"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="O74" s="2"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="O75" s="2"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="O76" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/rtss-pre1917/src/main/resources/csk-dvizhenie-evropriskoi-chasti-rossii/PatchYearData.xlsx
+++ b/rtss-pre1917/src/main/resources/csk-dvizhenie-evropriskoi-chasti-rossii/PatchYearData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-pre1917\src\main\resources\csk-dvizhenie-evropriskoi-chasti-rossii\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\csk-dvizhenie-evropriskoi-chasti-rossii\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF58A4D7-0D58-4A7A-B564-5B1DAEC751C5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{874F3728-A659-48E1-8EAF-902773E8D8C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10890" yWindow="2235" windowWidth="24945" windowHeight="21255" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{616F1713-D655-41CB-BC70-D2B5ECB02997}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="1" r:id="rId1"/>
@@ -139,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -148,26 +148,23 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -187,9 +184,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -227,7 +224,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -333,7 +330,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -475,7 +472,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -484,9 +481,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E727C47-D865-4836-8CF2-7B9647F06C78}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -499,15 +496,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5AD7F50-502A-4E44-B9E1-3028D5075735}">
   <dimension ref="A1:U76"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="5" width="18.28515625" customWidth="1"/>
-    <col min="6" max="6" width="16.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.83984375" customWidth="1"/>
+    <col min="3" max="3" width="11.68359375" customWidth="1"/>
+    <col min="4" max="5" width="18.26171875" customWidth="1"/>
+    <col min="6" max="6" width="16.68359375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="4" t="s">
         <v>3</v>
       </c>
@@ -527,7 +524,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -535,7 +532,7 @@
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="8" t="s">
         <v>14</v>
       </c>
@@ -549,7 +546,7 @@
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="8" t="s">
         <v>14</v>
       </c>
@@ -563,11 +560,11 @@
       <c r="E4" s="10"/>
       <c r="F4" s="7"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="7">
         <v>1903</v>
       </c>
       <c r="C5" s="2">
@@ -579,55 +576,55 @@
       <c r="E5" s="10"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="7">
         <v>1904</v>
       </c>
       <c r="C6" s="2">
-        <v>65477.5</v>
+        <v>65478</v>
       </c>
       <c r="D6" s="2">
-        <v>47868.5</v>
+        <v>47869</v>
       </c>
       <c r="E6" s="10"/>
       <c r="F6" s="7"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="7">
         <v>1905</v>
       </c>
       <c r="C7" s="2">
         <v>65509</v>
       </c>
       <c r="D7" s="2">
-        <v>45467.5</v>
+        <v>45468</v>
       </c>
       <c r="E7" s="10"/>
       <c r="F7" s="7"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="7">
         <v>1906</v>
       </c>
       <c r="C8" s="2">
         <v>66434</v>
       </c>
       <c r="D8" s="2">
-        <v>37380.5</v>
+        <v>37381</v>
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="7"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="8" t="s">
         <v>15</v>
       </c>
@@ -643,7 +640,7 @@
       <c r="E9" s="10"/>
       <c r="F9" s="7"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="8" t="s">
         <v>15</v>
       </c>
@@ -657,7 +654,7 @@
       <c r="E10" s="10"/>
       <c r="F10" s="7"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="8" t="s">
         <v>16</v>
       </c>
@@ -673,7 +670,7 @@
       <c r="E11" s="10"/>
       <c r="F11" s="7"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="8" t="s">
         <v>17</v>
       </c>
@@ -689,7 +686,7 @@
       <c r="E12" s="10"/>
       <c r="F12" s="7"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="8" t="s">
         <v>18</v>
       </c>
@@ -701,7 +698,7 @@
       <c r="E13" s="10"/>
       <c r="F13" s="7"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="8" t="s">
         <v>18</v>
       </c>
@@ -713,7 +710,7 @@
       <c r="E14" s="10"/>
       <c r="F14" s="7"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="8" t="s">
         <v>18</v>
       </c>
@@ -725,7 +722,7 @@
       <c r="E15" s="10"/>
       <c r="F15" s="7"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="8" t="s">
         <v>18</v>
       </c>
@@ -737,7 +734,7 @@
       <c r="E16" s="10"/>
       <c r="F16" s="7"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="8" t="s">
         <v>19</v>
       </c>
@@ -751,7 +748,7 @@
       <c r="E17" s="10"/>
       <c r="F17" s="7"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="6"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -759,7 +756,7 @@
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="6"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -767,7 +764,7 @@
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="6"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -775,7 +772,7 @@
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -783,7 +780,7 @@
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="6"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -791,7 +788,7 @@
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -799,7 +796,7 @@
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="6"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -807,7 +804,7 @@
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="6"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -815,7 +812,7 @@
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="6"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -823,7 +820,7 @@
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="6"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
@@ -831,7 +828,7 @@
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="6"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -839,7 +836,7 @@
       <c r="E28" s="7"/>
       <c r="F28" s="7"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="6"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -847,7 +844,7 @@
       <c r="E29" s="7"/>
       <c r="F29" s="7"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="6"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
@@ -855,7 +852,7 @@
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="6"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
@@ -863,7 +860,7 @@
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="6"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
@@ -871,7 +868,7 @@
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="6"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
@@ -879,7 +876,7 @@
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="6"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
@@ -887,7 +884,7 @@
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="6"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
@@ -895,7 +892,7 @@
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -903,7 +900,7 @@
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -911,42 +908,42 @@
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>10</v>
       </c>
@@ -957,7 +954,7 @@
       <c r="O48" s="3"/>
       <c r="P48" s="2"/>
     </row>
-    <row r="49" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
       <c r="G49" s="2"/>
@@ -969,7 +966,7 @@
       <c r="O49" s="3"/>
       <c r="P49" s="2"/>
     </row>
-    <row r="50" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="G50" s="2"/>
@@ -981,7 +978,7 @@
       <c r="O50" s="3"/>
       <c r="P50" s="2"/>
     </row>
-    <row r="51" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="G51" s="2"/>
@@ -993,7 +990,7 @@
       <c r="O51" s="3"/>
       <c r="P51" s="2"/>
     </row>
-    <row r="52" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="G52" s="2"/>
@@ -1003,7 +1000,7 @@
       <c r="O52" s="3"/>
       <c r="P52" s="2"/>
     </row>
-    <row r="53" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
       <c r="G53" s="2"/>
@@ -1019,7 +1016,7 @@
       <c r="T53" s="2"/>
       <c r="U53" s="2"/>
     </row>
-    <row r="54" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="G54" s="2"/>
@@ -1027,7 +1024,7 @@
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
     </row>
-    <row r="55" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="G55" s="2"/>
@@ -1038,7 +1035,7 @@
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
     </row>
-    <row r="56" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="G56" s="2"/>
@@ -1046,7 +1043,7 @@
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
     </row>
-    <row r="57" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="G57" s="2"/>
@@ -1056,7 +1053,7 @@
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
     </row>
-    <row r="58" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="G58" s="2"/>
@@ -1066,7 +1063,7 @@
       <c r="K58" s="2"/>
       <c r="L58" s="2"/>
     </row>
-    <row r="59" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
       <c r="G59" s="2"/>
@@ -1076,7 +1073,7 @@
       <c r="K59" s="2"/>
       <c r="L59" s="2"/>
     </row>
-    <row r="60" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="G60" s="2"/>
@@ -1086,7 +1083,7 @@
       <c r="K60" s="5"/>
       <c r="L60" s="5"/>
     </row>
-    <row r="61" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
       <c r="G61" s="2"/>
@@ -1096,7 +1093,7 @@
       <c r="K61" s="2"/>
       <c r="L61" s="2"/>
     </row>
-    <row r="62" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
       <c r="G62" s="2"/>
@@ -1106,7 +1103,7 @@
       <c r="K62" s="2"/>
       <c r="L62" s="2"/>
     </row>
-    <row r="63" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
       <c r="G63" s="2"/>
@@ -1116,7 +1113,7 @@
       <c r="K63" s="5"/>
       <c r="L63" s="5"/>
     </row>
-    <row r="64" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
       <c r="G64" s="2"/>
@@ -1126,7 +1123,7 @@
       <c r="K64" s="2"/>
       <c r="L64" s="2"/>
     </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
       <c r="G65" s="2"/>
@@ -1135,7 +1132,7 @@
       <c r="J65" s="2"/>
       <c r="O65" s="2"/>
     </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
       <c r="G66" s="2"/>
@@ -1146,7 +1143,7 @@
       <c r="L66" s="2"/>
       <c r="O66" s="2"/>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
@@ -1158,7 +1155,7 @@
       <c r="L67" s="2"/>
       <c r="O67" s="2"/>
     </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
@@ -1170,30 +1167,30 @@
       <c r="L68" s="2"/>
       <c r="O68" s="2"/>
     </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="K69" s="5"/>
       <c r="L69" s="5"/>
       <c r="O69" s="2"/>
     </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="O70" s="2"/>
     </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="O71" s="2"/>
     </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="O72" s="2"/>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="O73" s="2"/>
     </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="O74" s="2"/>
     </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="O75" s="2"/>
     </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="O76" s="2"/>
     </row>
   </sheetData>
